--- a/PCB/solar-glow-drh-v3_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM.xlsx
@@ -1238,17 +1238,17 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Rail-clamp reference — TLV431B (±0.5%); sets the VS trip</t>
+          <t>Comparator + 1.242 V ref, open-drain</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Vref 1.24 V, ±0.5%</t>
+          <t>TLV3011AIDBVR</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>SOT-23 (DBZ)</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>TLV431BCDBZR</t>
+          <t>TLV3011AIDBVR</t>
         </is>
       </c>
       <c r="H14" s="16" t="n">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>B grade (tighter) for a predictable clamp. tlv431a-3.pdf is TI's combined A/B datasheet. DK verified 2026-07-02 (SOT-23-3, Active in TI ordering table). Note: C temp grade = 0-70 C, fine for card duty.</t>
+          <t>Rail-clamp comparator. Selected 2026-07-03 to REPLACE the TLV431B: its uncommitted on-chip 1.242 V ref (init ±1%, 100 ppm/°C max drift) + ±10 pA input bias let the sense divider stay high-impedance (low standby drain) AND accurate — the TLV431 path was corrupted by its 0.5 µA Iref across the 1.8 M top resistor (up to 0.9 V of offset; the committed clamp actually sat ~3.74 V typ / ~4.5 V worst, over the 3.6 V accel &amp; NFC ceilings). Open-drain (needs the R9 pullup — reuses it). Iq 2.8 µA typ / 5 µA max, 1.8–5.5 V. DK page listing seen: "IC COMPARATOR 1 W/VOLT REF SOT23", TI, ACTIVE — confirm stock/price at cart. Use the commercial DBVR, NOT the -EP (DBVREP) automotive variant.</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>tlv431a-3.pdf</t>
+          <t>(TLV3011 datasheet — add to repo; TI SBOS303)</t>
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>296-17569-1-ND</t>
+          <t>296-TLV3011AIDBVR-ND (confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>1.8 MΩ, ±1%</t>
+          <t>1.82 MΩ, ±1%</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -1375,12 +1375,12 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>RC0402FR-071M82L</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>RC0402FR-071M8L</t>
+          <t>RC0402FR-071M82L</t>
         </is>
       </c>
       <c r="H16" s="16" t="n"/>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="K16" s="15" t="inlineStr">
         <is>
-          <t>Trip = 1.24×(1+R7/R8) = 3.47 V. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>Clamp divider top. 1.82 M chosen 2026-07-03 WITH R8=1.00 M and the TLV3011 ref to set the trip at the MAXIMUM rail the two 3.6 V-ceiling parts (LIS2DH12 accel, NT3H2211 NFC) allow: full worst-case stack (ref ±1% + 100 ppm/°C + resistors ±1%) lands VS ≤ 3.60 V at 25 °C (typ ~3.50 V). Deliberately on the ceiling to wring out storage energy (E∝V²). Hot-car note: at 85–105 °C worst-case creeps to ~3.61–3.65 V, still ~1 V under both parts’ 4.6/4.8 V ABSOLUTE-max damage line — safe, just briefly outside the operating window. Clamp equation VS = 1.242·(1+R7/R8); high-Z divider OK now that Iref is gone (TLV3011 IB ±10 pA → 18 µV, negligible). Format-derived DK — confirm at cart.</t>
         </is>
       </c>
       <c r="L16" s="13" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>RC0402FR-071M8L-ND (format-derived — confirm at cart)</t>
+          <t>RC0402FR-071M82L-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>Divider midpoint (CLREF) → TLV431 ref. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>Clamp divider bottom, 1.00 M (unchanged). Fixed leg of the TLV3011 trip divider: VS = 1.242·(1+R7/R8) with R7=1.82 M → VS ≤ 3.60 V worst-case. Format-derived DK — confirm at cart.</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">

--- a/PCB/solar-glow-drh-v3_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>TLV3011AIDBVR</t>
+          <t>TLV3011BIDBVR</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -1258,14 +1258,14 @@
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>TLV3011AIDBVR</t>
+          <t>TLV3011BIDBVR</t>
         </is>
       </c>
       <c r="H14" s="16" t="n">
-        <v>0.4</v>
+        <v>2.78</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>0.4</v>
+        <v>2.78</v>
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
@@ -1274,17 +1274,17 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>Rail-clamp comparator. Selected 2026-07-03 to REPLACE the TLV431B: its uncommitted on-chip 1.242 V ref (init ±1%, 100 ppm/°C max drift) + ±10 pA input bias let the sense divider stay high-impedance (low standby drain) AND accurate — the TLV431 path was corrupted by its 0.5 µA Iref across the 1.8 M top resistor (up to 0.9 V of offset; the committed clamp actually sat ~3.74 V typ / ~4.5 V worst, over the 3.6 V accel &amp; NFC ceilings). Open-drain (needs the R9 pullup — reuses it). Iq 2.8 µA typ / 5 µA max, 1.8–5.5 V. DK page listing seen: "IC COMPARATOR 1 W/VOLT REF SOT23", TI, ACTIVE — confirm stock/price at cart. Use the commercial DBVR, NOT the -EP (DBVREP) automotive variant.</t>
+          <t>Rail-clamp comparator. B-grade TLV3011B chosen 2026-07-04 over the A: HALF the input offset (6 mV vs 12 mV max) tightens the clamp trip, LOWER Iq (3.1 uA vs 5 uA max) cuts standby drain off the supercaps, and it adds integrated hysteresis + fail-safe inputs + POR (all B-only) so a slow rail crossing wont chatter. Uncommitted on-chip 1.242 V ref (init +-1%, 100 ppm/degC max drift) + 10 pA input bias let the sense divider stay high-Z AND accurate. REPLACES the TLV431B whose 0.5 uA Iref across the 1.8 M top R pushed the real clamp to ~3.74 V typ / ~4.5 V worst (over the 3.6 V accel &amp; NFC ceilings). Open-drain OUT (reuses the R9 pullup), supply 1.65-5.5 V. Verified on CSV: SOT-23-6, 2,123 in stock, $2.78, ACTIVE. Datasheet in repo (tlv3011b.pdf). Pinout (SOT-23-6): 1=V+ 2=REF 3=IN- 4=GND 5=OUT 6=IN+.</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>(TLV3011 datasheet — add to repo; TI SBOS303)</t>
+          <t>tlv3011b.pdf (repo; TI SBOS300C)</t>
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>296-TLV3011AIDBVR-ND (confirm at cart)</t>
+          <t>296-TLV3011BIDBVRCT-ND (cut tape; verified on CSV)</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v3_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM.xlsx
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>1.82 MΩ, ±1%</t>
+          <t>6.81 MΩ, ±1%</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>RC0402FR-071M82L</t>
+          <t>RC0402FR-076M81L</t>
         </is>
       </c>
       <c r="H16" s="16" t="n"/>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="K16" s="15" t="inlineStr">
         <is>
-          <t>Clamp divider top. 1.82 M chosen 2026-07-03 WITH R8=1.00 M and the TLV3011 ref to set the trip at the MAXIMUM rail the two 3.6 V-ceiling parts (LIS2DH12 accel, NT3H2211 NFC) allow: full worst-case stack (ref ±1% + 100 ppm/°C + resistors ±1%) lands VS ≤ 3.60 V at 25 °C (typ ~3.50 V). Deliberately on the ceiling to wring out storage energy (E∝V²). Hot-car note: at 85–105 °C worst-case creeps to ~3.61–3.65 V, still ~1 V under both parts’ 4.6/4.8 V ABSOLUTE-max damage line — safe, just briefly outside the operating window. Clamp equation VS = 1.242·(1+R7/R8); high-Z divider OK now that Iref is gone (TLV3011 IB ±10 pA → 18 µV, negligible). Format-derived DK — confirm at cart.</t>
+          <t>Clamp divider top. Raised 2026-07-04 from 1.82 M to 6.81 M (with R8 3.74 M) to cut standby drain. Ratio 1.821 is unchanged, so the worst-case clamp stays 3.60 V (ref +-1% + 100 ppm/degC + resistor +-1%); trip is ratio-dependent, not value-dependent. WHY now possible: the TLV3011 comparator input bias is +-10 pA, so the IB*R7 offset is ~68 uV (negligible) even at 6.81 M -- the old TLV431 could not do this (its 0.5 uA Iref across 1.8 M was ~0.9 V of error, forcing low impedance). Benefit: the divider is the ONLY continuous passive drain off the supercaps; at ~3.5 V it drops from 1.24 uA to 0.33 uA (-73%). Stayed at 6.81 M (not 9.76 M) to keep margin below where PCB surface leakage perturbs a high-Z node. Hot-car note (unchanged, ratio-set): 85-105 degC worst-case ~3.61-3.65 V, still ~1 V under the 4.6/4.8 V absolute-max. Format-derived DK -- confirm at cart.</t>
         </is>
       </c>
       <c r="L16" s="13" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>RC0402FR-071M82L-ND (format-derived — confirm at cart)</t>
+          <t>RC0402FR-076M81L-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>1 MΩ, ±1%</t>
+          <t>3.74 MΩ, ±1%</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML</t>
+          <t>RC0402FR-073M74L</t>
         </is>
       </c>
       <c r="H17" s="16" t="n"/>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>Clamp divider bottom, 1.00 M (unchanged). Fixed leg of the TLV3011 trip divider: VS = 1.242·(1+R7/R8) with R7=1.82 M → VS ≤ 3.60 V worst-case. Format-derived DK — confirm at cart.</t>
+          <t>Clamp divider bottom. Raised 2026-07-04 from 1.00 M to 3.74 M in step with R7 (6.81 M) to lower standby drain while holding the 1.821 ratio (worst-case clamp 3.60 V unchanged). Fixed leg of VS = 1.242*(1+R7/R8). Format-derived DK -- confirm at cart.</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML-ND (format-derived — confirm at cart)</t>
+          <t>RC0402FR-073M74L-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v3_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM.xlsx
@@ -636,15 +636,15 @@
     <row r="4" ht="23.25" customHeight="1" s="11">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>D1, D9</t>
+          <t>D1, D9, D10, D11</t>
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Per-panel blocking Schottky (VIN/VINB→VS); isolates cells + caps in the dark</t>
+          <t>Blocking Schottky (D1/D9, VIN·VINB→VS); comparator-supply diode-OR (D10/D11, VIN·VINB→VCMP)</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -671,7 +671,7 @@
         <v>0.37</v>
       </c>
       <c r="I4" s="16" t="n">
-        <v>0.74</v>
+        <v>1.48</v>
       </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
       </c>
       <c r="K4" s="15" t="inlineStr">
         <is>
-          <t>Low-Vf for the ~4 V solar; one per panel so a half-shadow can't back-feed. DK P/N re-verified verbatim 2026-07-02 ($0.37 @ 1). Non-G MMSD301T1 is obsolete (Rochester stock only) - keep the G.</t>
+          <t>Low-Vf for the ~4 V solar; one per panel so a half-shadow can't back-feed. DK P/N re-verified verbatim 2026-07-02 ($0.37 @ 1). Non-G MMSD301T1 is obsolete (Rochester stock only) - keep the G. D10/D11 added 2026-07-04: OR of VIN+VINB → VCMP powers clamp comparator U4 only while a panel produces (0 dark drain); same qualified MPN, qty 2→4.</t>
         </is>
       </c>
       <c r="L4" s="13" t="inlineStr">
@@ -1763,15 +1763,15 @@
     <row r="23" ht="15" customHeight="1" s="11">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C7, C10</t>
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Clamp local decoupling</t>
+          <t>Clamp local decoupling (C7 on VS; C10 on VCMP at U4 V+)</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -1798,7 +1798,7 @@
         <v>0.1</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="K23" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] C10 added 2026-07-04: 100 nF VCMP decoupling for the comparator (U4 now panel-powered via D10/D11).</t>
         </is>
       </c>
       <c r="L23" s="13" t="inlineStr">
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="I46" s="10" t="n">
-        <v>93.25</v>
+        <v>94.09</v>
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
@@ -3102,7 +3102,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>

--- a/PCB/solar-glow-drh-v3_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="10" min="1" max="1"/>
@@ -1125,29 +1125,29 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>I²C 0x18, ±2–16 g</t>
+          <t>I²C 0x1D, ±2–8 g</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>LGA-12 (2×2×1.0 mm)</t>
+          <t>LGA-12 CC-12-4 (2.2×2.3×0.87 mm)</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>LIS2DH12TR</t>
+          <t>ADXL367BCCZ-RL7</t>
         </is>
       </c>
       <c r="H12" s="16" t="n">
-        <v>1.79</v>
+        <v>7.5</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>1.79</v>
+        <v>7.5</v>
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
-          <t>CS→VS (I²C mode), SDO/SA0→GND (addr 0x18). SCL=PC3, SDA=PC2. DK verified 2026-07-02: 12-LGA (2x2), $1.79 @ 1, 40k stock.</t>
+          <t>SCLK→GND (I²C); ASEL (pin 3)→GND ⇒ addr 0x1D. FOOTPRINT = placeholder ST land re-netted by pin #; swap ADI CC-12-4 land before fab.</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>en.DM00091513.pdf</t>
+          <t>datasheets/adxl367.pdf</t>
         </is>
       </c>
       <c r="M12" s="13" t="inlineStr">
         <is>
-          <t>497-14851-2-ND (T&amp;R form observed; pick CT at cart)</t>
+          <t>(by MPN)</t>
         </is>
       </c>
     </row>
@@ -1763,20 +1763,20 @@
     <row r="23" ht="15" customHeight="1" s="11">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>C7, C10</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Clamp local decoupling (C7 on VS; C10 on VCMP at U4 V+)</t>
+          <t>Accelerometer VREG_OUT decoupling (mandatory)</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>0.2 µF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRM155 224 (0.22 µF) — verify</t>
         </is>
       </c>
       <c r="H23" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="K23" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] C10 added 2026-07-04: 100 nF VCMP decoupling for the comparator (U4 now panel-powered via D10/D11).</t>
+          <t>ADXL367 pin 9 VREG_OUT1 → GND. Datasheet-mandated 0.2 µF; 0.22 µF nearest std.</t>
         </is>
       </c>
       <c r="L23" s="13" t="inlineStr">
@@ -1817,14 +1817,14 @@
       </c>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>(by MPN)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="23.25" customHeight="1" s="11">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>SJ1</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="B24" s="14" t="n">
@@ -1832,91 +1832,95 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>VDDIO2 tie — bonds VDDIO2 to VS (MVIO unused)</t>
+          <t>Accelerometer VDDIO decoupling</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>0 Ω jumper</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>RC0805JR-070RL</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J24" s="13" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="K24" s="15" t="n"/>
+      <c r="K24" s="15" t="inlineStr">
+        <is>
+          <t>ADXL367 pin 12 VDDIO → GND.</t>
+        </is>
+      </c>
       <c r="L24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>RC0805JR-070RL-ND (format-derived — confirm at cart)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="25" ht="23.25" customHeight="1" s="11">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>SW2</t>
+          <t>C7, C10</t>
         </is>
       </c>
       <c r="B25" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>LED master switch — OFF / ON / TINY (solder-bridge)</t>
+          <t>Clamp local decoupling (C7 on VS; C10 on VCMP at U4 V+)</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>3-pad bridge</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>solder-bridge</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>(none — PCB bridge)</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="H25" s="16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
@@ -1925,70 +1929,66 @@
       </c>
       <c r="K25" s="15" t="inlineStr">
         <is>
-          <t>ANODE common; bridge to VS (ON) or via R12 (TINY); open = OFF (hardware off).</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] C10 added 2026-07-04: 100 nF VCMP decoupling for the comparator (U4 now panel-powered via D10/D11).</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="11">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>SB1–SB4</t>
+          <t>SJ1</t>
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Per-LED force-on jumpers (bridge to force a channel on)</t>
+          <t>VDDIO2 tie — bonds VDDIO2 to VS (MVIO unused)</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>solder-bridge</t>
+          <t>0 Ω jumper</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>solder-bridge</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>(none — PCB bridge)</t>
+          <t>RC0805JR-070RL</t>
         </is>
       </c>
       <c r="H26" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J26" s="13" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="K26" s="15" t="inlineStr">
-        <is>
-          <t>Open = normal MCU control. Bridge to force that LED hard-on, bypassing the MCU.</t>
-        </is>
-      </c>
+      <c r="K26" s="15" t="n"/>
       <c r="L26" s="13" t="inlineStr">
         <is>
           <t>—</t>
@@ -1996,14 +1996,14 @@
       </c>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RC0805JR-070RL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="23.25" customHeight="1" s="11">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>TC1</t>
+          <t>SW2</t>
         </is>
       </c>
       <c r="B27" s="14" t="n">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Tag-Connect TC2030 programming footprint (UPDI)</t>
+          <t>LED master switch — OFF / ON / TINY (solder-bridge)</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>TC2030-MCP-FP</t>
+          <t>3-pad bridge</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>TC2030 legged land</t>
+          <t>solder-bridge</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>(no part — pogo interface)</t>
+          <t>(none — PCB bridge)</t>
         </is>
       </c>
       <c r="H27" s="16" t="n">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="K27" s="15" t="inlineStr">
         <is>
-          <t>Hands-free UPDI; pairs with a TC2030-MCP cable.</t>
+          <t>ANODE common; bridge to VS (ON) or via R12 (TINY); open = OFF (hardware off).</t>
         </is>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
-          <t>TC2030-MCP.pdf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="13" t="inlineStr">
@@ -2064,25 +2064,25 @@
     <row r="28" ht="15" customHeight="1" s="11">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>SB1–SB4</t>
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>UPDI header (backup to TC1)</t>
+          <t>Per-LED force-on jumpers (bridge to force a channel on)</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>1×3, 0.1″</t>
+          <t>solder-bridge</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>0.1″ THT pads</t>
+          <t>solder-bridge</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>(unpopulated / 0.1″ header)</t>
+          <t>(none — PCB bridge)</t>
         </is>
       </c>
       <c r="H28" s="16" t="n">
@@ -2103,308 +2103,308 @@
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>Open = normal MCU control. Bridge to force that LED hard-on, bypassing the MCU.</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="11">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>TC1</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Tag-Connect TC2030 programming footprint (UPDI)</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>TC2030-MCP-FP</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>TC2030 legged land</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>(no part — pogo interface)</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="K29" s="15" t="inlineStr">
+        <is>
+          <t>Hands-free UPDI; pairs with a TC2030-MCP cable.</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>TC2030-MCP.pdf</t>
+        </is>
+      </c>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="23.25" customHeight="1" s="11">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>UPDI header (backup to TC1)</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>1×3, 0.1″</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>0.1″ THT pads</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>(unpopulated / 0.1″ header)</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
           <t>OPTIONAL</t>
         </is>
       </c>
-      <c r="K28" s="15" t="inlineStr">
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>Populate a 3-pin header if not using the Tag-Connect.</t>
         </is>
       </c>
-      <c r="L28" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="11">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="23.25" customHeight="1" s="11">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>JP1</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Bench pad strip — GND / VS / SCL / SDA probe pads (bench power injection + I²C tap)</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>4× bare SMD pads</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>1.7 mm sq, 2.54 mm pitch, B side</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>(bare pads — no component)</t>
         </is>
       </c>
-      <c r="H29" s="10" t="n">
+      <c r="H31" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="10" t="n">
+      <c r="I31" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="10" t="inlineStr">
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>NO PART</t>
         </is>
       </c>
-      <c r="K29" s="10" t="inlineStr">
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>v3.0 addition at (48.4, 14.54–22.16). Nothing to buy or place — mark DNP in the CPL. Pinout + bench ritual in solar-glow-drh-v2-hardware.md.</t>
         </is>
       </c>
-      <c r="L29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="23.25" customHeight="1" s="11">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="11">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>TP1</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
+      <c r="B32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>VIN test pad (pre-D1 solar node) — charge test / panel emulation</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>1× bare SMD pad</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>1.7 mm sq, B side</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>(bare pad — no component)</t>
         </is>
       </c>
-      <c r="H30" s="10" t="n">
+      <c r="H32" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I32" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>NO PART</t>
         </is>
       </c>
-      <c r="K30" s="10" t="inlineStr">
+      <c r="K32" s="10" t="inlineStr">
         <is>
           <t>v3.0 addition at (48.4, 12.0). Mark DNP in the CPL.</t>
         </is>
       </c>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="23.25" customHeight="1" s="11">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>MH1–MH4</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t>M2 mounting holes (grounded), board corners</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>2.2 mm plated</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>(no part — drill)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K31" s="15" t="inlineStr">
-        <is>
-          <t>Ties a metal back-plate to GND if enclosed; user-supplied M2 hardware.</t>
-        </is>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M31" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="11">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>U5</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>NFC tag — NTAG I²C plus 2K; phone reads/writes EEPROM, FD signals field to MCU</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>NTAG I²C plus, 2 KB, I²C 0x55</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>XQFN8 (SOT902-3, 1.6×1.6×0.5 mm)</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr">
-        <is>
-          <t>NXP</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>NT3H2211W0FHKH</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="I32" s="16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K32" s="15" t="inlineStr">
-        <is>
-          <t>v2.2 NFC addition. XQFN8 = SOT902-3 (datasheet Table 1). I²C 0x55 (no clash w/ accel 0x18). VCC→VS; VOUT pin 7 unconnected. Confirm live price. DK page verified 2026-07-02 (XFQFN8 exposed pad, $1.38 @ 1); Mouser cross: 771-NT3H2211W0FHKH, 9k stock.</t>
-        </is>
-      </c>
-      <c r="L32" s="13" t="inlineStr">
-        <is>
-          <t>NT3H2111_2211.pdf</t>
-        </is>
-      </c>
-      <c r="M32" s="13" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN)</t>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="11">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>MH1–MH4</t>
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>NFC tag (U5) VCC decoupling</t>
+          <t>M2 mounting holes (grounded), board corners</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>2.2 mm plated</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>(no part — drill)</t>
         </is>
       </c>
       <c r="H33" s="16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
@@ -2413,24 +2413,24 @@
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
-          <t>v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>Ties a metal back-plate to GND if enclosed; user-supplied M2 hardware.</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="11">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B34" s="14" t="n">
@@ -2438,121 +2438,121 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>NFC antenna trim — DNP (U5's internal 50 pF tunes the coil)</t>
+          <t>NFC tag — NTAG I²C plus 2K; phone reads/writes EEPROM, FD signals field to MCU</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>DNP (NP0/C0G land)</t>
+          <t>NTAG I²C plus, 2 KB, I²C 0x55</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>0402 (NP0/C0G land)</t>
+          <t>XQFN8 (SOT902-3, 1.6×1.6×0.5 mm)</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NXP</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>(DNP — not ordered)</t>
+          <t>NT3H2211W0FHKH</t>
         </is>
       </c>
       <c r="H34" s="16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="I34" s="16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="J34" s="13" t="inlineStr">
         <is>
-          <t>DNP</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="K34" s="15" t="inlineStr">
         <is>
-          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D. FERRITE SCENARIO (FER1 adopted): the 364006 sheet (0.38 mm stack, µ′~100-150 class ferrite) against the coil raises L above bare (~1.1-1.4×) and masks the floor -&gt; C9 ≈ 52-77 pF est., 68/82 the likely rungs; same ladder covers all three builds. Final trim always with the full stack (brace + ferrite + shell) installed.</t>
+          <t>v2.2 NFC addition. XQFN8 = SOT902-3 (datasheet Table 1). I²C 0x55 (no clash w/ accel 0x1D). VCC→VS; VOUT pin 7 unconnected. Confirm live price. DK page verified 2026-07-02 (XFQFN8 exposed pad, $1.38 @ 1); Mouser cross: 771-NT3H2211W0FHKH, 9k stock.</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NT3H2111_2211.pdf</t>
         </is>
       </c>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="23.85" customHeight="1" s="11">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>NFC antenna — PCB coil (LA/LB routed copper, F+B)</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>2.76 µH design value</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>PCB copper — no package</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>(no part — PCB feature)</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>NO PART</t>
-        </is>
-      </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>Sch-only symbol, no footprint. Inductance set by copper geometry; C9 land reserved for bench trim against it. Nothing to order or place.</t>
-        </is>
-      </c>
-      <c r="L35" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M35" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>NFC tag (U5) VCC decoupling</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>100 nF, X7R, 16 V</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="K35" s="15" t="inlineStr">
+        <is>
+          <t>v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]</t>
+        </is>
+      </c>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>(Murata GRM155 family)</t>
+        </is>
+      </c>
+      <c r="M35" s="13" t="inlineStr">
+        <is>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="11">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B36" s="14" t="n">
@@ -2560,39 +2560,43 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>NFC FD pull-up — open-drain FD (U5 pin 4) → PA6</t>
+          <t>NFC antenna trim — DNP (U5's internal 50 pF tunes the coil)</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>10 kΩ, ±1%</t>
+          <t>DNP (NP0/C0G land)</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0402 (NP0/C0G land)</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>RC0402FR-0710KL</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="n"/>
-      <c r="I36" s="16" t="n"/>
+          <t>(DNP — not ordered)</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="K36" s="15" t="inlineStr">
         <is>
-          <t>v2.2 NFC addition. Pulls open-drain FD up to VS. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D. FERRITE SCENARIO (FER1 adopted): the 364006 sheet (0.38 mm stack, µ′~100-150 class ferrite) against the coil raises L above bare (~1.1-1.4×) and masks the floor -&gt; C9 ≈ 52-77 pF est., 68/82 the likely rungs; same ladder covers all three builds. Final trim always with the full stack (brace + ferrite + shell) installed.</t>
         </is>
       </c>
       <c r="L36" s="13" t="inlineStr">
@@ -2602,14 +2606,14 @@
       </c>
       <c r="M36" s="13" t="inlineStr">
         <is>
-          <t>RC0402FR-0710KL-ND (format-derived — confirm at cart)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
@@ -2617,138 +2621,178 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>NFC VNFC load switch — power-gates U5 VCC from PA7 (NFC_EN)</t>
+          <t>NFC antenna — PCB coil (LA/LB routed copper, F+B)</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>High-side load switch</t>
+          <t>2.76 µH design value</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>SOT-23-6 (DBV)</t>
+          <t>PCB copper — no package</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>TPS22918DBVR</t>
+          <t>(no part — PCB feature)</t>
         </is>
       </c>
       <c r="H37" s="10" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
+          <t>NO PART</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>Sch-only symbol, no footprint. Inductance set by copper geometry; C9 land reserved for bench trim against it. Nothing to order or place.</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="11">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>NFC FD pull-up — open-drain FD (U5 pin 4) → PA6</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>10 kΩ, ±1%</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>RC0402FR-0710KL</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="n"/>
+      <c r="I38" s="16" t="n"/>
+      <c r="J38" s="13" t="inlineStr">
+        <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/tps22918.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off.</t>
-        </is>
-      </c>
-      <c r="L37" s="10" t="inlineStr">
-        <is>
-          <t>tps22918.pdf</t>
-        </is>
-      </c>
-      <c r="M37" s="10" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="11">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>NFC_EN pulldown — holds U6 OFF while PA7 tristates (UPDI / reset / brown-out)</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>100 kΩ, ±1%</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>Yageo</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>RC0402FR-07100KL</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I38" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t>v3.0 addition, placed with the R14 board patch at (4.39, 29.4). DK verified 2026-07-02: RC0402FR-07100KL-ND (CT, Active, $0.10 @ 1); legacy 311-100KLRCT-ND also live.</t>
-        </is>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M38" s="10" t="inlineStr">
-        <is>
-          <t>RC0402FR-07100KL-ND</t>
+      <c r="K38" s="15" t="inlineStr">
+        <is>
+          <t>v2.2 NFC addition. Pulls open-drain FD up to VS. [v3.0: 0402 to match board land; price TBC]</t>
+        </is>
+      </c>
+      <c r="L38" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="13" t="inlineStr">
+        <is>
+          <t>RC0402FR-0710KL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
-        </is>
+          <t>NFC VNFC load switch — power-gates U5 VCC from PA7 (NFC_EN)</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>High-side load switch</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>SOT-23-6 (DBV)</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>TPS22918DBVR</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>0.55</v>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/tps22918.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off.</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>tps22918.pdf</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>PRG1</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
@@ -2756,144 +2800,112 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
+          <t>NFC_EN pulldown — holds U6 OFF while PA7 tristates (UPDI / reset / brown-out)</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Adafruit UPDI Friend</t>
+          <t>100 kΩ, ±1%</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>26.4×17.8 mm board + JST-SH lead</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Adafruit</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>RC0402FR-07100KL</t>
         </is>
       </c>
       <c r="H40" s="10" t="n">
-        <v>6.95</v>
+        <v>0.1</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>6.95</v>
+        <v>0.1</v>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
+          <t>v3.0 addition, placed with the R14 board patch at (4.39, 29.4). DK verified 2026-07-02: RC0402FR-07100KL-ND (CT, Active, $0.10 @ 1); legacy 311-100KLRCT-ND also live.</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>(guide linked in firmware/README)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M40" s="10" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
+          <t>RC0402FR-07100KL-ND</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>CBL1</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
-        <v>1</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>TC2030-MCP (legged, RJ12 end)</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>6-ft cable, 6P6C modular plug</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>Tag-Connect</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>TC2030-MCP</t>
+          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
           <t>AUX</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback.</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="inlineStr">
-        <is>
-          <t>TC2030-MCP.pdf</t>
-        </is>
-      </c>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>HW1</t>
+          <t>PRG1</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
+          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
+          <t>Adafruit UPDI Friend</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>head ⌀3.8 × 1.4 mm</t>
+          <t>26.4×17.8 mm board + JST-SH lead</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>DIN 84 M2×3 brass</t>
-        </is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>6.95</v>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
@@ -2902,24 +2914,24 @@
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
+          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
-          <t>docs/screw-m2x3-cheese.png</t>
+          <t>(guide linked in firmware/README)</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>ENC1</t>
+          <t>CBL1</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
@@ -2927,27 +2939,27 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
+          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V, 3.55 mm stack</t>
+          <t>TC2030-MCP (legged, RJ12 end)</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>CNC from enclosure/ STEP</t>
+          <t>6-ft cable, 6P6C modular plug</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>(PCBWay CNC or equiv.)</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>(order from enclosure/*.step)</t>
+          <t>TC2030-MCP</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
@@ -2957,42 +2969,42 @@
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
+          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback.</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>enclosure/README.md</t>
+          <t>TC2030-MCP.pdf</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>INS1</t>
+          <t>HW1</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>~0.05 mm polyimide, die-cut to board outline</t>
+          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>sheet / die-cut</t>
+          <t>head ⌀3.8 × 1.4 mm</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
@@ -3002,22 +3014,22 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>(polyimide film, 0.05 mm)</t>
+          <t>DIN 84 M2×3 brass</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>AUX-OPTIONAL</t>
+          <t>AUX</t>
         </is>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>docs/screw-m2x3-cheese.png</t>
         </is>
       </c>
       <c r="M44" s="10" t="inlineStr">
@@ -3029,7 +3041,7 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>FER1</t>
+          <t>ENC1</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
@@ -3037,73 +3049,184 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
+          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Ti-6Al-4V, 3.55 mm stack</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>CNC from enclosure/ STEP</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>(PCBWay CNC or equiv.)</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>(order from enclosure/*.step)</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>enclosure/README.md</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>INS1</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>~0.05 mm polyimide, die-cut to board outline</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>sheet / die-cut</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>(generic)</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>(polyimide film, 0.05 mm)</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>AUX-OPTIONAL</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>FER1</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
           <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>WE-FSFS material 364 (13.56 MHz grade), 0.38 mm overall stack, cut to 12.2 × 25.8 mm</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>Würth Elektronik</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>364006</t>
         </is>
       </c>
-      <c r="H45" s="10" t="n">
+      <c r="H47" s="10" t="n">
         <v>17.43</v>
       </c>
-      <c r="I45" s="10" t="n">
+      <c r="I47" s="10" t="n">
         <v>17.43</v>
       </c>
-      <c r="J45" s="10" t="inlineStr">
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>AUX</t>
         </is>
       </c>
-      <c r="K45" s="10" t="inlineStr">
+      <c r="K47" s="10" t="inlineStr">
         <is>
           <t>FINAL, verified 2026-07-03: DK 732-5049-ND, Active, tray, $17.43 @ 1 (51 in stock at verification; 24-wk mfr lead — buy with the order). 60×60 mm sheet, 0.38 mm overall stack (ferrite ~0.3 + PET + non-conductive single-sided PSA); one sheet = 4 patches. Cut 12.2 × 25.8 mm on the 2 mm score grid; brace channel depth = measured stack − 0.05 (sits ~0.05 proud, seats flush; PET face to the board, PSA into the brace). Stock-dry fallback: 3× stacked 3641014 (732-13935-ND, $4.19 ea, µ′150/µ″3 @ 13.56 MHz, 0.14 mm ea) ≈ same ferrite thickness; last resort Laird MHLL6060-300 (240-2791-ND, 0.09 mm, weakest). All three datasheets in repo.</t>
         </is>
       </c>
-      <c r="L45" s="10" t="inlineStr">
+      <c r="L47" s="10" t="inlineStr">
         <is>
           <t>Worth ferrite sheet .pdf + Ferrite layer 2.pdf + Laird ferrite.pdf (repo)</t>
         </is>
       </c>
-      <c r="M45" s="10" t="inlineStr">
+      <c r="M47" s="10" t="inlineStr">
         <is>
           <t>732-5049-ND</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="G46" s="10" t="inlineStr">
+    <row r="48">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
         </is>
       </c>
-      <c r="I46" s="10" t="n">
-        <v>94.09</v>
-      </c>
-      <c r="K46" s="10" t="inlineStr">
-        <is>
-          <t>Sum of the 28 priced Ext$ cells only — several converted lines remain unpriced pending quotes; see footnote.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="19" t="inlineStr">
+      <c r="I48" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>Sum of the 30 priced Ext$ cells only — several converted lines remain unpriced pending quotes; see footnote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).</t>
         </is>

--- a/PCB/solar-glow-drh-v3_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>PointLED 2-SMD flat-lead, ~3.4×1.25 mm</t>
+          <t>SMD, 3.4x1.9 mm</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-071M82L</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>GRM155 224 (0.22 µF) — verify</t>
+          <t>GRM155R71C224KA12D</t>
         </is>
       </c>
       <c r="H23" s="14" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>GRM155R61A475ME15D</t>
+          <t>GRM155R61A475MEAAD</t>
         </is>
       </c>
       <c r="H37" s="14" t="n"/>
@@ -2633,13 +2633,13 @@
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>NEW bulk at the LED anode (LED side of SW2). ~3 uF effective at ~3.4 V after DC-bias derate = ~3x the C4 bulk. Place ~(20, 47.9) B.Cu, south of the window. Bench-gate: only load-bearing if the glow visibly modulates VS. 4.7 uF X5R 0402 10V is a real, stocked part; GRM155R61A475ME15D is format-derived from the Murata convention — confirm exact suffix/availability at cart (Samsung CL05A475M* / Yageo CC0402 equiv all fine).</t>
+          <t>NEW bulk at the LED anode (LED side of SW2). ~3 uF effective at ~3.4 V after DC-bias derate = ~3x the C4 bulk. Place ~(20, 47.9) B.Cu, south of the window. Bench-gate: only load-bearing if the glow visibly modulates VS. 4.7 uF X5R 0402 10V is a real, stocked part; GRM155R61A475MEAAD is format-derived from the Murata convention — confirm exact suffix/availability at cart (Samsung CL05A475M* / Yageo CC0402 equiv all fine).</t>
         </is>
       </c>
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>GRM155R61A475ME15D-ND (format-derived — confirm at cart)</t>
+          <t>GRM155R61A475MEAAD-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v3_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOLAR-GLOW DRH v3.0 BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SOLAR-GLOW DRH v3.0 BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>10 nF, X7R, 16 V</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C103KA01D</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="H11" s="14" t="n"/>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>RC filter on the VSENSE node. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>RC filter on the VSENSE node. [v3.0: 0402 to match board land; price TBC] [consolidation: 10nF -&gt; 100nF, joins the 100 nF group]</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>1 µF, X5R, 10 V</t>
+          <t>4.7 µF, X5R, 10 V</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>GRM155R61A105KE15D</t>
+          <t>GRM155R61A475MEAAD</t>
         </is>
       </c>
       <c r="H21" s="14" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] [consolidation: 1 µF -&gt; 4.7 µF, same part as C13]</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
@@ -1865,11 +1865,11 @@
     <row r="25" ht="23.25" customHeight="1" s="9">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>C7, C10</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] C10 added 2026-07-04: 100 nF VCMP decoupling for the comparator (U4 now panel-powered via D10/D11).</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] C10 added 2026-07-04: 100 nF VCMP decoupling for the comparator (U4 now panel-powered via D10/D11). [C10 -&gt; DNP in consolidation: VCMP decoupling not strictly required]</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
@@ -2742,12 +2742,12 @@
       <c r="I39" s="14" t="n"/>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>v2.2 NFC addition. Pulls open-drain FD up to VS. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>v2.2 NFC addition. Pulls open-drain FD up to VS. [v3.0: 0402 to match board land; price TBC] [consolidation: DNP, internal PA6 pull-up covers FD]</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>100 kΩ, ±1%</t>
+          <t>1 MΩ, ±1%</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-07100KL</t>
+          <t>RC0402FR-071ML</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition, placed with the R14 board patch at (4.39, 29.4). DK verified 2026-07-02: RC0402FR-07100KL-ND (CT, Active, $0.10 @ 1); legacy 311-100KLRCT-ND also live.</t>
+          <t>v3.0 addition, placed with the R14 board patch at (4.39, 29.4). DK verified 2026-07-02: RC0402FR-07100KL-ND (CT, Active, $0.10 @ 1); legacy 311-100KLRCT-ND also live. [consolidation: 100 kΩ -&gt; 1 MΩ, joins the R5/R6 reel]</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
@@ -3257,7 +3257,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51" ht="360.4" customHeight="1" s="9">
       <c r="A51" s="15" t="inlineStr">
         <is>
